--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0036.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0036.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Spectro Drake</t>
+          <t>Drake Spectro</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Havoc Drake</t>
+          <t>Drake Hỗn Loạn</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Devotee's Flesh</t>
+          <t>Thịt Tín Đồ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Abyssal Gunmaster</t>
+          <t>Thợ Súng Vực Sâu</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Spearback</t>
+          <t>Lưng Lao</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Carapace</t>
+          <t>Vỏ giáp</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Lãnh Đạo Lưu Đày</t>
+          <t>Thủ Lĩnh Lưu Đày</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Exile Technician</t>
+          <t>Kỹ Sư Lưu Đày</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Fractsidus Executioner</t>
+          <t>Đao Phủ Fractsidus</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hoochief Menace</t>
+          <t>Hăm Dọa Thủ Lĩnh Hoo</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Autopuppet Scout</t>
+          <t>Trinh Sát Tự Động</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Nâng cấp tất cả Core Echoes</t>
+          <t>Nâng cấp toàn bộ Lõi Echo.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Thu thập 6 Huy chương Uy danh</t>
+          <t>Thu thập 6 Huy Chương Uy Tín</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Thu thập 12 Huy chương Uy danh</t>
+          <t>Thu thập 12 Huy Chương Danh Vọng</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Đánh bại Lupa trong trận đấu Peaks of Prestige</t>
+          <t>Đánh bại Lupa trong trận đấu tại Đỉnh Vinh Quang</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Đánh bại Calcharo trong trận đấu Peaks of Prestige</t>
+          <t>Đánh bại Calcharo trong trận đấu tại Đỉnh Danh Vọng.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách Vô tận - Độ khó Khó một lần</t>
+          <t>Hoàn thành Thử Thách Vô Tận - Độ Khó một lần</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Đạt kỷ lục cao nhất 1.000 Fame Flags</t>
+          <t>Lập kỷ lục mới với 1.000 Cờ Danh Vọng</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 2</t>
+          <t>Đạt Cấp Bậc 2</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 3</t>
+          <t>Đạt Cấp Bậc 3</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 4</t>
+          <t>Đạt Cấp Bậc 4</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 5</t>
+          <t>Đạt Cấp Bậc 5</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 6</t>
+          <t>Đạt Cấp Bậc 6</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 7</t>
+          <t>Đạt Cấp Bậc 7</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 8</t>
+          <t>Đạt Cấp Bậc 8</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 9</t>
+          <t>Đạt Cấp Bậc 9</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Mở khóa 40 thẻ</t>
+          <t>Mở khóa 40 thẻ bài</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Mở khóa 60 thẻ</t>
+          <t>Mở khóa 60 thẻ bài</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Mở khóa 80 thẻ</t>
+          <t>Mở khóa 80 thẻ bài</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Mở khóa 90 thẻ</t>
+          <t>Mở khóa 90 thẻ bài</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Mở khóa 10 thẻ bằng Điểm Uy danh</t>
+          <t>Mở khóa 10 thẻ với Điểm Uy Tín</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Mở khóa 20 thẻ bằng Điểm Uy danh</t>
+          <t>Mở khóa 20 thẻ bằng Điểm Uy Danh</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 10</t>
+          <t>Đạt Cấp Bậc 10</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Lumiscale Construct</t>
+          <t>Cấu Trúc Vảy Quang</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Fractsidus Thruster</t>
+          <t>Động Cơ Phản Lực Fractsidus</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Vitreum Dancer</t>
+          <t>Vũ Công Pha Lê</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Rage Against the Statue</t>
+          <t>Nổi Giận Trước Bức Tượng</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Hurriclaw</t>
+          <t>Vuốt Bão Cuồng</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Pilgrim's Shell</t>
+          <t>Vỏ Sò Hành Hương</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Flamecrest Gladiator</t>
+          <t>Dũng Sĩ Flamecrest</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Galecrest Gladiator</t>
+          <t>Dũng Sĩ Gale Crest</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Lightcrest Gladiator</t>
+          <t>Dũng Sĩ Lightcrest</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Frostcrest Gladiator</t>
+          <t>Đấu Sĩ Sương Tuyết</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Thundercrest Gladiator</t>
+          <t>Dũng Sĩ Đỉnh Sấm</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Gladiators of Septimont chiến đấu không giới hạn, thi triển sức mạnh bão tố</t>
+          <t>Những đấu sĩ Septimont chiến đấu không giới hạn, thi triển sức mạnh gió bão.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Abysscrest Gladiator</t>
+          <t>Đấu Sĩ Abysscrest</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Fractsidus Inspector</t>
+          <t>Thanh Tra Fractsidus</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Cetus the Tidebreaker</t>
+          <t>Cetus Kẻ Phá Thủy Triều</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Scar: Aberrant Nightmare</t>
+          <t>Scar: Ác Mộng Dị Biệt</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Nhận tất cả Core Echo</t>
+          <t>Thu thập tất cả Core Echoes</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Đánh bại Brant trong trận đấu Peaks of Prestige</t>
+          <t>Đánh bại Brant trong trận đấu tại Đỉnh Danh Vọng.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Fallacy of Không Return</t>
+          <t>Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Galescourge Stalker</t>
+          <t>Thợ Săn Gale Scourge</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Voltscourge Stalker</t>
+          <t>Kẻ Rình Rập Sét Tàn Phá</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Frostscourge Stalker</t>
+          <t>Kẻ Rình Rập Băng Giá</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Chop Chop: Leftless</t>
+          <t>Chop Chop: Không Tay Trái</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Chop Chop: Rightless</t>
+          <t>Chop Chop: Không Tay Phải</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Nimbus Wraith</t>
+          <t>Hồn Ma Nimbus</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Hocus Pocus</t>
+          <t>Ảo thuật biến!</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Diggy Duggy</t>
+          <t>Đào Đi Đào Đi</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Chest Mimic</t>
+          <t>Rương Biến Hình</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Questless Knight</t>
+          <t>Hiệp Sĩ Không Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Diurnus Knight</t>
+          <t>Hiệp Sĩ Diurnus</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Nocturnus Knight</t>
+          <t>Hiệp Sĩ Nocturnus</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Abyssal Patricius</t>
+          <t>Quý Tộc Vực Sâu</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Abyssal Gladius</t>
+          <t>Kiếm Vực Sâu</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Abyssal Mercator</t>
+          <t>Thương Nhân Vực Sâu</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Chop Chop</t>
+          <t>Nhanh lên nào</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Dragon of Dirge</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nightmare: Feilian Beringal</t>
+          <t>Ác Mộng: Feilian Beringal</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Nightmare: Impermanence Heron</t>
+          <t>Ác Mộng: Impermanence Heron</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Nightmare: Thundering Mephis</t>
+          <t>Ác Mộng: Thundering Mephis</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Nightmare: Tempest Mephis</t>
+          <t>Ác Mộng: Tempest Mephis</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Nightmare: Crownless</t>
+          <t>Ác Mộng: Crownless</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Nightmare: Inferno Rider</t>
+          <t>Ác Mộng: Inferno Rider</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Nightmare: Mourning Aix</t>
+          <t>Ác Mộng: Mourning Aix</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Reminiscence: Fleurdelys</t>
+          <t>Hồi ức: Fleurdelys</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Nightmare: Lampylumen Myriad</t>
+          <t>Ác Mộng: Lampylumen Myriad</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Nightmare: Kelpie</t>
+          <t>Ác Mộng: Ngựa Nước Kelpie</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Lioness of Glory</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Reminiscence: Fenrico</t>
+          <t>Hồi ức: Fenrico</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Nightmare: Hecate</t>
+          <t>Ác Mộng: Hecate</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Nightmare: Tambourinist</t>
+          <t>Ác Mộng: Tambourinist</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Nightmare: Havoc Warrior</t>
+          <t>Ác Mộng: Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Nightmare: Glacio Predator</t>
+          <t>Ác Mộng: Thú Dữ Băng Giá</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Nightmare: Violet-Feathered Heron</t>
+          <t>Ác Mộng: Violet-Feathered Heron</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Nightmare: Cyan-Feathered Heron</t>
+          <t>Ác Mộng: Cyan-Feathered Heron</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Nightmare: Electro Predator</t>
+          <t>Ác Mộng: Thú Dữ Điện Quang</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Nightmare: Aero Predator</t>
+          <t>Ác Mộng: Thú Dữ Aero</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Nightmare: Gulpuff</t>
+          <t>Ác Mộng: Gulpuff</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Nightmare: Chirpuff</t>
+          <t>Ác Mộng: Chirpuff</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>The False Sovereign</t>
+          <t>Kẻ Quân Vương Giả Mạo</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Lady of the Sea</t>
+          <t>Nữ Thần Biển Cả</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Midnight Ranger</t>
+          <t>Kỵ Sĩ Bóng Đêm</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Midnight Ranger</t>
+          <t>Kỵ Sĩ Bóng Đêm</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Gang Member</t>
+          <t>Thành Viên Bang</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Nightmare: Baby Viridblaze Saurian</t>
+          <t>Ác Mộng: Baby Viridblaze Saurian</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Nightmare: Baby Roseshroom</t>
+          <t>Ác Mộng: Baby Roseshroom</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Tremor Warrior</t>
+          <t>Chiến Binh Rung Chấn</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Nightmare: Tick Tack</t>
+          <t>Ác Mộng: Tick Tack</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Nightmare: Dwarf Cassowary</t>
+          <t>Ác Mộng: Đà Điểu Lùn</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Flora Drone</t>
+          <t>Drone Flora</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Mining Drone</t>
+          <t>Drone Khai Thác</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Geospider S4</t>
+          <t>Nhện Địa Chấn S4</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Outcast Executioner</t>
+          <t>Đao phủ Kẻ bị ruồng bỏ</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Thundstaff Outcast</t>
+          <t>Kẻ Lưu Đày Gậy Sấm</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Nightmare: Roseshroom</t>
+          <t>Ác Mộng: Roseshroom</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Nightmare: Viridblaze Saurian</t>
+          <t>Ác Mộng: Viridblaze Saurian</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Twin Nova: Nebulous Cannon</t>
+          <t>Song Tinh: Đại Bác Vụ Nổ</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade</t>
+          <t>Tân Tinh Song Sinh: Kiếm Hố Đen</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Flora Reindeer</t>
+          <t>Tuần Lộc Flora</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Ironhoof</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Sabercat Reaver</t>
+          <t>Kẻ Tàn Sát Mèo Đao</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Sabercat Prowler</t>
+          <t>Kẻ Rình Rập Mèo Đao</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Frostbite Coleoid</t>
+          <t>Mực Băng Giá Coleoid</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Windlash Coleoid</t>
+          <t>Mực Gió Giật</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Scar: Lightbane Reversal</t>
+          <t>Scar: Đảo Ngược Ánh Sáng</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Reminiscence: Threnodian - Leviathan</t>
+          <t>Hồi ức: Threnodian - Leviathan</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Voidworm</t>
+          <t>Giun Voidworm</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Iceglint Dancer</t>
+          <t>Vũ Công Băng Giá</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Shadow Stepper</t>
+          <t>Bước Bóng</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Kronablight</t>
+          <t>Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Reminiscence: Kronaclaw</t>
+          <t>Hồi ức: Kronaclaw</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Kronaclaw</t>
+          <t>Móng Vuốt Hắc Ám</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Fractsidus Ripper</t>
+          <t>Kẻ Xé Nát Fractsidus</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Fractsidus Mawdoll</t>
+          <t>Mawdoll Fractsidus</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Fractsidus Milliner</t>
+          <t>Thợ Mũ Fractsidus</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Phagosite: Bipolarch</t>
+          <t>Phagosite: Song Cực Thạch</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Phagosite: Hysterarch</t>
+          <t>Phagosite: Hysteriarch</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Phagosite: Miserarch</t>
+          <t>Phagosite: Miseriarch</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Voidwing Moth</t>
+          <t>Bướm Voidwing</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Aleph-1's Creation</t>
+          <t>Sáng Tạo của Aleph-1</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Reminiscence: Denia</t>
+          <t>Hồi ức: Denia</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Lone Mandarin - Discovered placeholder</t>
+          <t>Quan Lại Cô Đơn - Phát hiện placeholder</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Phantom: Mourning Aix</t>
+          <t>Hồn Ma: Mourning Aix</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Whining Aix - Underdiscovered placeholder</t>
+          <t>Aix Rên Rỉ - Chưa khám phá (placeholder)</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Rocksteady Guardian-Discovered placeholder</t>
+          <t>Vệ Binh Vững Chãi - Chưa Khám Phá</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Phantom: Rocksteady Guardian</t>
+          <t>Hồn Ma: Rocksteady Guardian</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Rocksteady Guardian-Underdiscovered placeholder</t>
+          <t>Vệ Binh Vững Chãi - Chưa Khám Phá Hoàn Toàn</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Hoartoise-Discoverd placeholder</t>
+          <t>Hoartoise - Chưa Khám Phá (placeholder)</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Hoartoise-Underdiscovered placeholder</t>
+          <t>Hoartoise - Chưa Khám Phá Hoàn Toàn (placeholder)</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Thundering Mephis-Discovered placeholder</t>
+          <t>Mephis Sấm Sét - Đã phát hiện</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Thundering Mephis-Underdiscovered placeholder</t>
+          <t>Mephis Sấm Sét - Chưa phát hiện</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Feilian Beringal - Discovered placeholder</t>
+          <t>Feilian Beringal - Đã phát hiện</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Feilian Beringal - Underdiscovered placeholder</t>
+          <t>Feilian Beringal - Chưa được khám phá</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Phantom: Clang Bang</t>
+          <t>Bóng Ma: Clang Bang</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Phantom: Lightcrusher</t>
+          <t>Phantom: Đè Ánh Sáng</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Phantom: Dreamless</t>
+          <t>Bóng Ma: Dreamless</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Phantom: Lumiscale Construct</t>
+          <t>Hồn Ma: Lumiscale Construct</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Capitaneus - Discovered placeholder</t>
+          <t>Capitaneus - Đã phát hiện</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Phantom: Capitaneus</t>
+          <t>Bóng Ma: Capitaneus</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Capitaneus - Undiscovered placeholder</t>
+          <t>Capitaneus - Chưa phát hiện</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Phantom: Nimbus Wraith</t>
+          <t>Hồn Ma: Bóng Ma Mây Đen</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Phantom: Crownless</t>
+          <t>Bóng Ma: Crownless</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Phantom: Nightmare Crownless</t>
+          <t>Hồn Ma: Nightmare Crownless</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Phantom: Chest Mimic</t>
+          <t>Bóng Ma: Hộp Giả Mạo</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Phantom: Fae Ignis</t>
+          <t>Bóng Ma: Fae Ignis</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Phantom: Cuddle Wuddle</t>
+          <t>Bóng Ma: Ôm Ấm</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Phantom: Nightmare Inferno Rider</t>
+          <t>Hồn Ma: Nightmare Inferno Rider</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Phantom: Nightmare Mourning Aix</t>
+          <t>Hồn Ma: Nightmare Mourning Aix</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Phantom: Fallacy of Không Return</t>
+          <t>Phantom: Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Phantom: Lioness of Glory</t>
+          <t>Phantom: Sư Tử Hào Quang</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Phantom: Chop Chop</t>
+          <t>Bóng Ma: Chặt Chém</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Phantom: The False Sovereign</t>
+          <t>Phantom: Quân Vương Giả</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Phantom: Twin Nova - Nebulous Cannon</t>
+          <t>Phantom: Song Tinh Vân - Đại Bác Tinh Vân</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Phantom: Twin Nova - Collapsar Blade</t>
+          <t>Phantom: Song Tinh Vân - Kiếm Hố Đen</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Huyễn Ảnh: Sigillum</t>
+          <t>Phantom: Ấn Kết</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Phantom: Iceglint Dancer</t>
+          <t>Phantom: Vũ Công Băng Giá</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Bóng Ma: Lớp Vỏ Lò Phản Ứng</t>
+          <t>Hồn Ma: Xác Sống Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Đồng bằng Trung tâm</t>
+          <t>Central Plains</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Hẻm Núi Linh Hồn</t>
+          <t>Gorges of Spirits</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Rừng Tối</t>
+          <t>Dim Forest</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Cao nguyên Desorock</t>
+          <t>Desorock Highland</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Đô thị Hoang Phế</t>
+          <t>Thành Phố Hoang Phí</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Bãi Lầy Whining Aix</t>
+          <t>Whining Aix's Mire</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Class (COST 1)</t>
+          <t>Hạng Tiêu Chuẩn (CHI PHÍ 1)</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Elite Class (COST 3)</t>
+          <t>Hạng Tinh Anh (CHI PHÍ 3)</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Overlord Class (COST 4)</t>
+          <t>Hạng Chúa Tể (CHI PHÍ 4)</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Calamity Class (COST 4)</t>
+          <t>Hạng Tai Họa (CHI PHÍ 4)</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Required Material</t>
+          <t>Vật liệu cần thiết</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Chi phí điều chỉnh sử dụng Echoes giống nhau</t>
+          <t>Điều Chỉnh tiêu tốn Echo tương tự</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Moonlit Path Event Rewards Removal</t>
+          <t>Gỡ Bỏ Phần Thưởng Sự Kiện Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Wuthering Waves Dev Đội</t>
+          <t>Đội Ngũ Phát Triển Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Moonlit Path Event Rewards Removal</t>
+          <t>Gỡ Bỏ Phần Thưởng Sự Kiện Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>New Mail Received</t>
+          <t>Thư Mới</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Khu Vực An Toàn</t>
+          <t>Khu Vực Ổn Định</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Khu vực nguy hiểm</t>
+          <t>Khu vực Nguy hiểm</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Khu Vực Quá Tải</t>
+          <t>Vùng Tăng Tốc</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>New Tuning Slot</t>
+          <t>Khe Điều Chỉnh mới</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Connecting</t>
+          <t>Đang kết nối</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Tiger's Maw Ore</t>
+          <t>Quặng Hàm Hổ</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Tiger's Maw Eatery</t>
+          <t>Quán Ăn Hàm Hổ</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Yibai Clinic</t>
+          <t>Phòng Khám Yibai</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Intelligent Retrieval &amp; Indexing Hệ thống</t>
+          <t>Hệ Thống Truy Xuất &amp; Lập Chỉ Mục Thông Minh</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Trợ lý Điều dưỡng Tự động Nightingale</t>
+          <t>Hệ Thống Điều Dưỡng Tự Động Nightingale</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Royan Merchant</t>
+          <t>Thương nhân Roya</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Người Thu Thập Băng Ghi Lời Cuối Lahai-Roi</t>
+          <t>Người Sưu Tầm Băng Ghi Lời Cuối Lahai-Roi</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Soliskin Reunion</t>
+          <t>Đoàn Tụ Soliskin</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Lone Star</t>
+          <t>Ngôi Sao Cô Đơn</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Tự Động Hóa Hướng Dẫn &amp; Quản Lý Tín Hiệu Thông Minh</t>
+          <t>Tự động hóa Hướng dẫn &amp; Quản lý Tín hiệu Thông minh</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Prism Fruit Spectrometer</t>
+          <t>Máy Phân Tích Sắc Cầu</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Cấp độ Đầu bếp</t>
+          <t>Cấp Độ Đầu Bếp</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Cấp Độ Synthesis</t>
+          <t>Cấp Độ Tổng Hợp</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Crafting Table</t>
+          <t>Bàn chế tác</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Weapon Shop</t>
+          <t>Cửa Hàng Vũ Khí</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Shifang Pharmacy</t>
+          <t>Dược Phẩm Shifang</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Souvenir Cửa hàng</t>
+          <t>Cửa Hàng Lưu Niệm</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Waveplates  Exchange</t>
+          <t>Đổi Bảng Tần Số</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Mahe's Grocery</t>
+          <t>Cửa Hàng Tạp Hóa Mahe</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Panhua's Kitchen</t>
+          <t>Bếp Nhà Panhua</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Tiger's Maw Ore</t>
+          <t>Quặng Hàm Hổ</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Nhận tất cả Core Echo</t>
+          <t>Thu thập tất cả Core Echoes</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Septimont Sonance Casket Collector</t>
+          <t>Người Thu Thập Rương Sonance Septimont</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Tiger's Maw Eatery</t>
+          <t>Quán Ăn Hàm Hổ</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Yibai Clinic</t>
+          <t>Phòng Khám Yibai</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Yumyum Haven</t>
+          <t>Thiên Đường Ẩm Thực</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Fireworks Cửa hàng</t>
+          <t>Cửa tiệm pháo hoa</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Wishing Stall</t>
+          <t>Gian Hàng Ước Nguyện</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>KU-Money Exchange</t>
+          <t>Sàn Giao Dịch KU-Money</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Track 1</t>
+          <t>Bản nhạc 1</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Track 2</t>
+          <t>Bản nhạc 2</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Track 3</t>
+          <t>Bản nhạc 3</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Track 4</t>
+          <t>Bản nhạc 4</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Track 5</t>
+          <t>Bản nhạc 5</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Track 6</t>
+          <t>Bản nhạc 6</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Challenge Record</t>
+          <t>Hồ Sơ Thử Thách</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Phần Thưởng Hoàn Thành</t>
+          <t>Nhận Phần Thưởng Hoàn Thành</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Fashion Union</t>
+          <t>Liên Minh Thời Trang</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Đăng Ký Lunite</t>
+          <t>Lunite Subscription</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Bundles Cấp Độ</t>
+          <t>Gói Cấp độ</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Bundles</t>
+          <t>Gói Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>New Voyage Bundles</t>
+          <t>Gói Hành trình mới</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Tidal Exchange</t>
+          <t>Trao đổi Thủy Triều</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Adversity Exchange</t>
+          <t>Trao Đổi Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Simulation Training Cửa hàng</t>
+          <t>Kho Đồ Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Trial Cửa hàng</t>
+          <t>Kho Dữ Liệu Thử Nghiệm</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Trang phục Display</t>
+          <t>Trưng Bày Trang Phục</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Aspects</t>
+          <t>Thuộc Tính</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Được đề xuất</t>
+          <t>Đề xuất</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Fashion Union</t>
+          <t>Liên Minh Thời Trang</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Gói</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Trao đổi Vật Phẩm</t>
+          <t>Đổi vật phẩm</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Points Shop</t>
+          <t>Cửa Hàng Điểm</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Đánh bại Raul the Dustbound</t>
+          <t>Đánh bại Raul the Dustbound.</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Đánh bại Furius the Firebrand</t>
+          <t>Tiêu diệt Furius the Firebrand</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Đấu Sĩ 4</t>
+          <t>Đạt Cấp Đấu Thủ 4</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Đấu Sĩ 6</t>
+          <t>Đạt Cấp Độ Đấu Thủ 6</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Đấu Sĩ 8</t>
+          <t>Đạt Cấp Độ Đấu Thủ 8</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Đấu Sĩ 12</t>
+          <t>Đạt Cấp Đấu Thủ 12</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Outfits</t>
+          <t>Các Trang Phục</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Sao Chép ID</t>
+          <t>Sao chép ID</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Bỏ tắt tiếng</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Mute</t>
+          <t>Im lặng</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Chặn</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Báo cáo</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Đổi Ảnh đại diện</t>
+          <t>Đổi Nhân Vật</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Đổi Ấn</t>
+          <t>Chuyển Ấn Tượng</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Edit Name</t>
+          <t>Đổi tên</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Đánh bại Gallus the Nightmare</t>
+          <t>Đánh bại Gallus Ác Mộng</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Đấu Sĩ 2</t>
+          <t>Đạt Cấp Đấu Thủ 2</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Đấu Sĩ 10</t>
+          <t>Đạt Cấp Đấu Thủ 10</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Core Echo</t>
+          <t>Nâng cấp 1 Lõi Echo</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Thu thập 3 Huy Chương Uy Tín</t>
+          <t>Thu thập 3 Huy Chương Danh Vọng</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Đánh bại Ciaccona trong trận đấu tại Đỉnh Danh vọng</t>
+          <t>Đánh bại Ciaccona trong trận đấu tại Peaks of Prestige</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách Vô tận - Thường một lần</t>
+          <t>Hoàn thành Thử Thách Vô Tận - Bình Thường một lần</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Đạt kỷ lục cao 500 Cờ Fame</t>
+          <t>Lập kỷ lục mới với 500 Cờ Danh Vọng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Change Title</t>
+          <t>Đổi danh hiệu</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Trưng bày Resonator</t>
+          <t>Trình diễn Resonator</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Lộ Trình Sao Đan Xen</t>
+          <t>Những Con Đường Sao Đan Xen</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Character Model</t>
+          <t>Mô hình Nhân vật</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Hide</t>
+          <t>Ẩn</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Hiển thị</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Name Người chơi và UID</t>
+          <t>Tên và UID Người Chơi</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Hide</t>
+          <t>Ẩn</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Hiển thị</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Face the Camera</t>
+          <t>Hướng về máy quay</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Bật</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>DOF (Depth of Field)</t>
+          <t>Độ sâu trường ảnh (DOF)</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Bật</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Focal Distance</t>
+          <t>Khoảng Cách Tiêu Điểm</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Depth Blur Radius</t>
+          <t>Bán kính Mờ Sâu</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Item 1-Star</t>
+          <t>Vật phẩm 1 Sao</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>2-Stars trở xuống</t>
+          <t>2 Sao trở xuống</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>3-Stars trở xuống</t>
+          <t>3 Sao trở xuống</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>4-Stars trở xuống</t>
+          <t>Hạng 4 Sao và Thấp Hơn</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Unlimited</t>
+          <t>Không giới hạn</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Call back</t>
+          <t>Hãy gọi lại</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Trả lời đi</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>calling</t>
+          <t>gọi tên</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Quay lại on Shelf</t>
+          <t>Đặt lại chỗ cũ</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>On the shelf:</t>
+          <t>Trên kệ:</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Navigate</t>
+          <t>Định vị</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Maximum number reached</t>
+          <t>Đã đạt số lượng tối đa</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Ads &amp; Fraud</t>
+          <t>Quảng cáo &amp; Gian lận</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Porn &amp; Violence</t>
+          <t>Bạo Lực &amp; Khiêu Dâm</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Cheating</t>
+          <t>Gian lận</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Chính trường</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Cyberviolence</t>
+          <t>Bạo lực mạng</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Choose a reason to report</t>
+          <t>Chọn lý do báo cáo</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Nhận Metaphor: Key of Tranquility</t>
+          <t>Nhận Ẩn Dụ: Chìa Khóa Bình Yên</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Nhận 1 Metaphor Hiếm cấp 3</t>
+          <t>Nhận 1 Hiếm Hóa Cấp 3</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Perform a Character upgrade</t>
+          <t>Nâng cấp một Cộng Hưởng Giả</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Ký ức Hủy diệt</t>
+          <t>Ký Ức Của Thảm Họa</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Special Room found</t>
+          <t>Phòng Đặc Biệt đã phát hiện</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Dream Fragment Obtained</t>
+          <t>Đã thu thập Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Number of Metaphors Obtained</t>
+          <t>Số Ẩn Dụ Đã Thu Thập</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Insufficient Dream Fragments</t>
+          <t>Mảnh Giấc Mơ không đủ</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Chọn Mataphor</t>
+          <t>Chọn Ẩn Dụ</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Nhận Metaphor</t>
+          <t>Nhận Ẩn Dụ</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Chọn Metaphor</t>
+          <t>Chọn Ẩn Dụ</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Replace</t>
+          <t>Thay thế</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Tăng cường</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Tổng cộng</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Resonator Nâng cấp</t>
+          <t>Nâng Cấp Resonator</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Echo Replaced</t>
+          <t>Âm Hưởng Đã Thay Thế</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Replace Echo</t>
+          <t>Thay thế Echo</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Metaphor Obtained</t>
+          <t>Đã thu thập Ẩn Dụ</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>New Abilities Unlocked</t>
+          <t>Kỹ Năng Mới Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Current Echo</t>
+          <t>Echo Hiện Tại</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Current Resonator</t>
+          <t>Resonator hiện tại</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Echo Details</t>
+          <t>Thông Tin Tiếng Vọng</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Outline</t>
+          <t>Đường Viền</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Character replacement</t>
+          <t>Thay đổi nhân vật</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Chọn Echo</t>
+          <t>Chọn Tiếng Vọng</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Enhance Resonator</t>
+          <t>Nâng cấp Resonator</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Metaphor Obtained</t>
+          <t>Đã thu thập Ẩn Dụ</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Activated: {0}/{1}</t>
+          <t>Đã kích hoạt: {0}/{1}</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Insufficient Memory Points</t>
+          <t>Không đủ Điểm Bộ Nhớ.</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Not unlocked</t>
+          <t>Chưa mở khóa</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Hướng Dẫn</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Difficulty 1</t>
+          <t>Độ khó 1</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Difficulty 2</t>
+          <t>Độ khó 2</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Difficulty 3</t>
+          <t>Độ khó 3</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Difficulty 4</t>
+          <t>Độ khó 4</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Difficulty 5</t>
+          <t>Độ khó 5</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Difficulty VI</t>
+          <t>Độ Khó VI</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Cấp Độ Xây Dựng Metaphor</t>
+          <t>Cấp Độ Xây Dựng Ẩn Dụ</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Snow Waltz</t>
+          <t>Điệu Valse Tuyết</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Healing You'tan</t>
+          <t>Hồi phục You'tan</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Gallant Blaze</t>
+          <t>Lửa Dũng Mãnh</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Wooly-Counting Game</t>
+          <t>Trò Đếm Cừu Wooly</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dragon's Breath</t>
+          <t>Hơi Thở Rồng</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Lightning of Execution</t>
+          <t>Lưỡi Tia Chớp Tử Thần</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Fist of Thunder</t>
+          <t>Nắm Đấm Sấm Sét</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Jinhsi's Title</t>
+          <t>Danh hiệu của Jinhsi</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Sẽ cập nhật</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Breath of Winds</t>
+          <t>Hơi Gió Thổi</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
